--- a/Documentos/MIA — Serie histórica 2020-2026.xlsx
+++ b/Documentos/MIA — Serie histórica 2020-2026.xlsx
@@ -1993,7 +1993,7 @@
         <v>36.09</v>
       </c>
       <c r="F74" t="n">
-        <v>87.37</v>
+        <v>87.38</v>
       </c>
       <c r="G74" t="n">
         <v>67.39</v>
@@ -2018,7 +2018,7 @@
         <v>36.09</v>
       </c>
       <c r="F75" t="n">
-        <v>87.38</v>
+        <v>87.39</v>
       </c>
       <c r="G75" t="n">
         <v>67.68000000000001</v>
@@ -2068,7 +2068,7 @@
         <v>36.09</v>
       </c>
       <c r="F77" t="n">
-        <v>87.39</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="G77" t="n">
         <v>68.26000000000001</v>
@@ -2093,7 +2093,7 @@
         <v>36.09</v>
       </c>
       <c r="F78" t="n">
-        <v>87.40000000000001</v>
+        <v>87.41</v>
       </c>
       <c r="G78" t="n">
         <v>68.38</v>
@@ -2118,7 +2118,7 @@
         <v>35.29</v>
       </c>
       <c r="F79" t="n">
-        <v>87.40000000000001</v>
+        <v>87.42</v>
       </c>
       <c r="G79" t="n">
         <v>68.36</v>
@@ -2143,7 +2143,7 @@
         <v>34.5</v>
       </c>
       <c r="F80" t="n">
-        <v>87.41</v>
+        <v>87.43000000000001</v>
       </c>
       <c r="G80" t="n">
         <v>68.33</v>
@@ -3864,7 +3864,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>54.51</v>
+        <v>54.52</v>
       </c>
       <c r="C33" t="n">
         <v>50.81</v>
@@ -3891,7 +3891,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2026-08-18 16:41</t>
+          <t>2026-08-19 10:04</t>
         </is>
       </c>
     </row>
